--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_222_R23.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_222_R23.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0962</v>
+        <v>3.4766</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4995</v>
+        <v>5.0894</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5967</v>
+        <v>-1.6129</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6904</v>
+        <v>4.1399</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4791</v>
+        <v>1.4332</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2113</v>
+        <v>2.7067</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9372</v>
+        <v>7.1713</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7226</v>
+        <v>3.1999</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2146</v>
+        <v>3.9714</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2468</v>
+        <v>-3.0314</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2435</v>
+        <v>-1.7667</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0033</v>
+        <v>-1.2647</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7099</v>
+        <v>0.0325</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5623</v>
+        <v>-0.2985</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1476</v>
+        <v>0.331</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7785</v>
+        <v>3.0289</v>
       </c>
       <c r="E3" t="n">
-        <v>4.425</v>
+        <v>2.4995</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6465</v>
+        <v>0.5295</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1399</v>
+        <v>1.6904</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4332</v>
+        <v>0.4791</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7067</v>
+        <v>1.2113</v>
       </c>
       <c r="J3" t="n">
-        <v>7.1713</v>
+        <v>1.9372</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1999</v>
+        <v>0.7226</v>
       </c>
       <c r="L3" t="n">
-        <v>3.9714</v>
+        <v>1.2146</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.0314</v>
+        <v>-0.2468</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7667</v>
+        <v>-0.2435</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2647</v>
+        <v>-0.0033</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6959</v>
+        <v>0.6959</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6655</v>
+        <v>0.6427</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.963</v>
+        <v>0.5623</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2974</v>
+        <v>0.0804</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0252</v>
+        <v>1.7602</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5612</v>
+        <v>2.371</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5359</v>
+        <v>-0.6108</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.624</v>
+        <v>0.0723</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4261</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1979</v>
+        <v>-0.6056</v>
       </c>
       <c r="J4" t="n">
-        <v>1.722</v>
+        <v>2.4855</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9697</v>
+        <v>2.77</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2477</v>
+        <v>-0.2845</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.346</v>
+        <v>-2.4131</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.3958</v>
+        <v>-2.0921</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.3211</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0952</v>
+        <v>0.6183</v>
       </c>
       <c r="T4" t="n">
-        <v>0.767</v>
+        <v>-0.1687</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3282</v>
+        <v>0.787</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9304</v>
+        <v>0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5175</v>
+        <v>1.4423</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2963</v>
+        <v>2.8102</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7788</v>
+        <v>-1.3679</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0723</v>
+        <v>-1.624</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.4261</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6056</v>
+        <v>-1.1979</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4855</v>
+        <v>1.722</v>
       </c>
       <c r="K5" t="n">
-        <v>2.77</v>
+        <v>1.9697</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2845</v>
+        <v>-0.2477</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4131</v>
+        <v>-3.346</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0921</v>
+        <v>-2.3958</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3211</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3756</v>
+        <v>0.5122</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2434</v>
+        <v>0.016</v>
       </c>
       <c r="U5" t="n">
-        <v>0.619</v>
+        <v>0.4962</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1418</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0596</v>
+        <v>0.2517</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7016</v>
+        <v>2.2298</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6419</v>
+        <v>-1.978</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2362</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0638</v>
+        <v>1.256</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5059</v>
+        <v>1.0341</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5579</v>
+        <v>0.2219</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5361</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1774</v>
+        <v>-1.2714</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.2259</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1127</v>
+        <v>-1.0455</v>
       </c>
       <c r="G7" t="n">
         <v>-2.5037</v>
@@ -1000,13 +1000,13 @@
         <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5403</v>
+        <v>0.4463</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.094</v>
+        <v>-0.2552</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6344</v>
+        <v>0.7016</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9279</v>
+        <v>-1.6245</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6827</v>
+        <v>-0.5158</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2452</v>
+        <v>-1.1087</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6538</v>
+        <v>-2.2447</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1452</v>
+        <v>-1.9269</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5086000000000001</v>
+        <v>-0.3178</v>
       </c>
       <c r="J8" t="n">
-        <v>0.711</v>
+        <v>-0.8933</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3564</v>
+        <v>-0.8431</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3546</v>
+        <v>-0.0502</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0572</v>
+        <v>-1.3513</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2112</v>
+        <v>-1.0838</v>
       </c>
       <c r="O8" t="n">
-        <v>0.154</v>
+        <v>-0.2676</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.4071</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.217</v>
+        <v>0.5327</v>
       </c>
       <c r="T8" t="n">
-        <v>0.637</v>
+        <v>0.3776</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.42</v>
+        <v>0.1551</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0007</v>
+        <v>-1.7263</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5774</v>
+        <v>-1.6827</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4233</v>
+        <v>-0.0435</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4667</v>
+        <v>0.6538</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1656</v>
+        <v>0.1452</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3011</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0893</v>
+        <v>0.711</v>
       </c>
       <c r="K9" t="n">
-        <v>0.39</v>
+        <v>0.3564</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6993</v>
+        <v>0.3546</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.556</v>
+        <v>-0.0572</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5556</v>
+        <v>-0.2112</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0004</v>
+        <v>0.154</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-4.4071</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5381</v>
+        <v>0.4187</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.507</v>
+        <v>0.637</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0451</v>
+        <v>-0.2183</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7264</v>
+        <v>-2.3197</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4161</v>
+        <v>-0.4595</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3103</v>
+        <v>-1.8602</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2447</v>
+        <v>-1.4667</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9269</v>
+        <v>-1.1656</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3178</v>
+        <v>-0.3011</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8933</v>
+        <v>1.0893</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8431</v>
+        <v>0.39</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0502</v>
+        <v>0.6993</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3513</v>
+        <v>-2.556</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0838</v>
+        <v>-1.5556</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2676</v>
+        <v>-1.0004</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5693</v>
+        <v>0.2192</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>-0.389</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0466</v>
+        <v>0.6082</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.644600000000001</v>
+        <v>3.017799999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>11.7427</v>
+        <v>12.116</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.097900000000001</v>
+        <v>-9.098000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-1.518900000000001</v>
@@ -1282,7 +1282,7 @@
         <v>-2.3052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7863</v>
+        <v>0.7863000000000002</v>
       </c>
       <c r="J11" t="n">
         <v>17.2314</v>
@@ -1300,10 +1300,10 @@
         <v>-13.1968</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.5535</v>
+        <v>-5.553500000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-11.5977</v>
@@ -1312,13 +1312,13 @@
         <v>11.5979</v>
       </c>
       <c r="S11" t="n">
-        <v>4.305099999999999</v>
+        <v>4.678599999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.142</v>
+        <v>1.5156</v>
       </c>
       <c r="U11" t="n">
-        <v>3.163</v>
+        <v>3.1631</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1418</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4761</v>
+        <v>2.8973</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3166</v>
+        <v>2.9612</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1594</v>
+        <v>-0.0639</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6375</v>
+        <v>6.4148</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7646</v>
+        <v>2.6238</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1271</v>
+        <v>3.791</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3884</v>
+        <v>8.398899999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5122</v>
+        <v>3.7615</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1239</v>
+        <v>4.6374</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7509</v>
+        <v>-1.9841</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7477</v>
+        <v>-1.1377</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0033</v>
+        <v>-0.8464</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1598</v>
+        <v>-4.4071</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>-5.7988</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>0.604</v>
+        <v>-0.3244</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4481</v>
+        <v>-0.8529</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0521</v>
+        <v>0.5285</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3943</v>
+        <v>1.214</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5361</v>
+        <v>1.214</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2632</v>
+        <v>2.3309</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8433</v>
+        <v>2.3166</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.58</v>
+        <v>0.0142</v>
       </c>
       <c r="G13" t="n">
-        <v>6.4148</v>
+        <v>2.6375</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6238</v>
+        <v>2.7646</v>
       </c>
       <c r="I13" t="n">
-        <v>3.791</v>
+        <v>-0.1271</v>
       </c>
       <c r="J13" t="n">
-        <v>8.398899999999999</v>
+        <v>3.3884</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7615</v>
+        <v>3.5122</v>
       </c>
       <c r="L13" t="n">
-        <v>4.6374</v>
+        <v>-0.1239</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9841</v>
+        <v>-0.7509</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1377</v>
+        <v>-0.7477</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8464</v>
+        <v>-0.0033</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.4071</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.7988</v>
+        <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9586</v>
+        <v>0.4589</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9709</v>
+        <v>-0.4481</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0123</v>
+        <v>0.9069</v>
       </c>
       <c r="V13" t="n">
-        <v>1.214</v>
+        <v>0.3943</v>
       </c>
       <c r="W13" t="n">
-        <v>1.214</v>
+        <v>0.5361</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9452</v>
+        <v>1.3219</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7776</v>
+        <v>1.1314</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1676</v>
+        <v>0.1905</v>
       </c>
       <c r="G14" t="n">
         <v>0.2877</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3399</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.601</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8735000000000001</v>
+        <v>1.167</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0129</v>
+        <v>0.3857</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1394</v>
+        <v>0.7814</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2161</v>
+        <v>1.2035</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1259</v>
+        <v>-0.9915</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.3421</v>
+        <v>2.195</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9758</v>
+        <v>2.3157</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5781</v>
+        <v>0.0105</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6022999999999999</v>
+        <v>2.3053</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.192</v>
+        <v>-1.1122</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4522</v>
+        <v>-1.002</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7398</v>
+        <v>-0.1103</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0896</v>
+        <v>-0.5004</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0351</v>
+        <v>-0.7703</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1248</v>
+        <v>0.27</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4993</v>
+        <v>0.9686</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2677</v>
+        <v>2.659</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2316</v>
+        <v>-1.6904</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2035</v>
+        <v>-1.2161</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9915</v>
+        <v>1.1259</v>
       </c>
       <c r="I16" t="n">
-        <v>2.195</v>
+        <v>-2.3421</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3157</v>
+        <v>1.9758</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0105</v>
+        <v>2.5781</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3053</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1122</v>
+        <v>-3.192</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.002</v>
+        <v>-1.4522</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1103</v>
+        <v>-1.7398</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1681</v>
+        <v>0.1847</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8883</v>
+        <v>-0.389</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2798</v>
+        <v>0.5737</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3365</v>
+        <v>-0.2801</v>
       </c>
       <c r="E17" t="n">
         <v>-0.156</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1805</v>
+        <v>-0.1241</v>
       </c>
       <c r="G17" t="n">
         <v>1.5304</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3651</v>
+        <v>0.4215</v>
       </c>
       <c r="T17" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8132</v>
+        <v>0.8696</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9103</v>
+        <v>-1.6744</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.8464</v>
       </c>
       <c r="F18" t="n">
         <v>-2.5207</v>
@@ -1858,10 +1858,10 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.456</v>
+        <v>-0.2201</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U18" t="n">
         <v>-0.1573</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9975</v>
+        <v>-2.0818</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1199</v>
+        <v>0.002</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1174</v>
+        <v>-2.0838</v>
       </c>
       <c r="G19" t="n">
         <v>-3.5822</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3431</v>
+        <v>-0.4274</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4208</v>
+        <v>0.3029</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7639</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0.5361</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4055</v>
+        <v>-2.4841</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.732</v>
+        <v>-1.9679</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6734</v>
+        <v>-0.5162</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8001</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3734</v>
+        <v>-0.452</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1968</v>
+        <v>-0.0391</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5702</v>
+        <v>-0.4129</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.052</v>
+        <v>-3.2372</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.3836</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5535</v>
+        <v>-3.6207</v>
       </c>
       <c r="G21" t="n">
         <v>-4.1106</v>
@@ -2092,13 +2092,13 @@
         <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7248</v>
+        <v>-0.91</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0474</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7723</v>
+        <v>-0.8395</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5361</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6445</v>
+        <v>-1.0719</v>
       </c>
       <c r="E22" t="n">
-        <v>8.561900000000001</v>
+        <v>8.561999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.2063</v>
+        <v>-9.633699999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5189</v>
+        <v>1.518899999999999</v>
       </c>
       <c r="H22" t="n">
         <v>2.305200000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7864000000000004</v>
+        <v>-0.7864</v>
       </c>
       <c r="J22" t="n">
         <v>18.7501</v>
@@ -2161,7 +2161,7 @@
         <v>-6.339799999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.0001999999999995339</v>
+        <v>-0.000199999999999978</v>
       </c>
       <c r="Q22" t="n">
         <v>-11.5977</v>
@@ -2170,13 +2170,13 @@
         <v>11.5976</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.3052</v>
+        <v>-2.7324</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.1631</v>
+        <v>-3.163</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1421</v>
+        <v>0.4306</v>
       </c>
       <c r="V22" t="n">
         <v>0.1417999999999997</v>
